--- a/InputData/bldgs/RPbBCT/Rebate Perc by Building Component Type.xlsx
+++ b/InputData/bldgs/RPbBCT/Rebate Perc by Building Component Type.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27706"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\bldgs\RPbBCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5188199D-076B-459F-9A6C-A672B4FCF82B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5188199D-076B-459F-9A6C-A672B4FCF82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1335" yWindow="945" windowWidth="24765" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,20 @@
     <sheet name="Data" sheetId="8" r:id="rId2"/>
     <sheet name="RPbBCT" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,12 +40,138 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
+    <t>RPbBCT Rebate Percentage by Building Component Type</t>
+  </si>
+  <si>
     <t>Sources:</t>
   </si>
   <si>
+    <t>Main Data Source</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>State Energy-Efficient Appliance Rebate Program: Volume 1 - Program Design: Lessons Learned</t>
+  </si>
+  <si>
+    <t>https://www.energy.gov/sites/prod/files/2015/06/f23/SEEARP_volume_1_report_UPDATED%206-18-15.pdf</t>
+  </si>
+  <si>
+    <t>Page 11, Table 5</t>
+  </si>
+  <si>
+    <t>Alternate Data Source</t>
+  </si>
+  <si>
+    <t>Datta, S. and Gulati, S.</t>
+  </si>
+  <si>
+    <t>Utility Rebates for ENERGY STAR Appliances: Are They Effective?</t>
+  </si>
+  <si>
+    <t>https://ethz.ch/content/dam/ethz/special-interest/mtec/cepe/cepe-dam/documents/research/cepe-wp/CEPE_WP81.pdf</t>
+  </si>
+  <si>
+    <t>Page 11, Table 4</t>
+  </si>
+  <si>
     <t>About</t>
   </si>
   <si>
+    <t>The rebate policy in the EPS represents a rebate paid by utilities to customers who</t>
+  </si>
+  <si>
+    <t>buy more efficient building components (e.g. appliances, HVAC, water heaters, etc.)</t>
+  </si>
+  <si>
+    <t>In the U.S., we use SEEARP data, which was a government-funded rebate program,</t>
+  </si>
+  <si>
+    <t>due to good data availability.  However, a comparison to the rebate amounts paid</t>
+  </si>
+  <si>
+    <t>in an analysis of hundreds of utility-funded programs (Datta and Gulati) indicates</t>
+  </si>
+  <si>
+    <t>that the rebate percentages for utility-funded programs may be similar, or slightly</t>
+  </si>
+  <si>
+    <t>less generous.</t>
+  </si>
+  <si>
+    <t>Currency conversion</t>
+  </si>
+  <si>
+    <t>2003 to 2012 USD</t>
+  </si>
+  <si>
+    <t>State Energy Efficiency Appliance Rebate Program (SEEARP) Data</t>
+  </si>
+  <si>
+    <t>Assumed to be in 2012 dollars, since the State Energy Efficiency Appliance Rebate Program (SEEARP) being studied ran from 2010-2014</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Average Amount per Product</t>
+  </si>
+  <si>
+    <t>Average Sales Price</t>
+  </si>
+  <si>
+    <t>Average Rebate Percentage</t>
+  </si>
+  <si>
+    <t>Appliances*</t>
+  </si>
+  <si>
+    <t>HVAC</t>
+  </si>
+  <si>
+    <t>Water Heaters</t>
+  </si>
+  <si>
+    <t>* Appliances include clothes washers, dishwashers, freezers, refrigerators, and room air conditioners.</t>
+  </si>
+  <si>
+    <t>Datta and Gulati Data</t>
+  </si>
+  <si>
+    <t>Assumed to be in 2003 dollars, since the table is labeled as aggregating data from 2001-2006</t>
+  </si>
+  <si>
+    <t>Mean Amount per Product (2003 USD)</t>
+  </si>
+  <si>
+    <t>Mean Amount per Product (2012 USD)</t>
+  </si>
+  <si>
+    <t>Clothes Washers</t>
+  </si>
+  <si>
+    <t>Dishwashers</t>
+  </si>
+  <si>
+    <t>Refrigerators</t>
+  </si>
+  <si>
+    <t>We don't have the average purchase price of these appliances, so we don't know what percentage this represents.</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (rebate %)</t>
+  </si>
+  <si>
+    <t>urban residential</t>
+  </si>
+  <si>
+    <t>rural residential</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
     <t>heating</t>
   </si>
   <si>
@@ -56,132 +188,6 @@
   </si>
   <si>
     <t>other component</t>
-  </si>
-  <si>
-    <t>urban residential</t>
-  </si>
-  <si>
-    <t>rural residential</t>
-  </si>
-  <si>
-    <t>commercial</t>
-  </si>
-  <si>
-    <t>RPbBCT Rebate Percentage by Building Component Type</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (rebate %)</t>
-  </si>
-  <si>
-    <t>Datta, S. and Gulati, S.</t>
-  </si>
-  <si>
-    <t>Utility Rebates for ENERGY STAR Appliances: Are They Effective?</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/sites/prod/files/2015/06/f23/SEEARP_volume_1_report_UPDATED%206-18-15.pdf</t>
-  </si>
-  <si>
-    <t>Page 11, Table 5</t>
-  </si>
-  <si>
-    <t>State Energy-Efficient Appliance Rebate Program: Volume 1 - Program Design: Lessons Learned</t>
-  </si>
-  <si>
-    <t>U.S. Department of Energy</t>
-  </si>
-  <si>
-    <t>https://ethz.ch/content/dam/ethz/special-interest/mtec/cepe/cepe-dam/documents/research/cepe-wp/CEPE_WP81.pdf</t>
-  </si>
-  <si>
-    <t>The rebate policy in the EPS represents a rebate paid by utilities to customers who</t>
-  </si>
-  <si>
-    <t>buy more efficient building components (e.g. appliances, HVAC, water heaters, etc.)</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>HVAC</t>
-  </si>
-  <si>
-    <t>Water Heaters</t>
-  </si>
-  <si>
-    <t>Appliances*</t>
-  </si>
-  <si>
-    <t>* Appliances include clothes washers, dishwashers, freezers, refrigerators, and room air conditioners.</t>
-  </si>
-  <si>
-    <t>Average Amount per Product</t>
-  </si>
-  <si>
-    <t>Average Sales Price</t>
-  </si>
-  <si>
-    <t>Average Rebate Percentage</t>
-  </si>
-  <si>
-    <t>Datta and Gulati Data</t>
-  </si>
-  <si>
-    <t>Clothes Washers</t>
-  </si>
-  <si>
-    <t>Dishwashers</t>
-  </si>
-  <si>
-    <t>Refrigerators</t>
-  </si>
-  <si>
-    <t>Page 11, Table 4</t>
-  </si>
-  <si>
-    <t>Assumed to be in 2003 dollars, since the table is labeled as aggregating data from 2001-2006</t>
-  </si>
-  <si>
-    <t>Assumed to be in 2012 dollars, since the State Energy Efficiency Appliance Rebate Program (SEEARP) being studied ran from 2010-2014</t>
-  </si>
-  <si>
-    <t>Mean Amount per Product (2003 USD)</t>
-  </si>
-  <si>
-    <t>Mean Amount per Product (2012 USD)</t>
-  </si>
-  <si>
-    <t>Currency conversion</t>
-  </si>
-  <si>
-    <t>2003 to 2012 USD</t>
-  </si>
-  <si>
-    <t>Main Data Source</t>
-  </si>
-  <si>
-    <t>Alternate Data Source</t>
-  </si>
-  <si>
-    <t>We don't have the average purchase price of these appliances, so we don't know what percentage this represents.</t>
-  </si>
-  <si>
-    <t>State Energy Efficiency Appliance Rebate Program (SEEARP) Data</t>
-  </si>
-  <si>
-    <t>In the U.S., we use SEEARP data, which was a government-funded rebate program,</t>
-  </si>
-  <si>
-    <t>due to good data availability.  However, a comparison to the rebate amounts paid</t>
-  </si>
-  <si>
-    <t>in an analysis of hundreds of utility-funded programs (Datta and Gulati) indicates</t>
-  </si>
-  <si>
-    <t>that the rebate percentages for utility-funded programs may be similar, or slightly</t>
-  </si>
-  <si>
-    <t>less generous.</t>
   </si>
 </sst>
 </file>
@@ -192,9 +198,9 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,7 +341,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -354,16 +360,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="9"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -391,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -431,9 +434,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -466,26 +469,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -518,26 +504,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -712,130 +681,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="58.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="6">
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="B12" s="6">
         <v>2011</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="14">
+        <v>1.2477934782608695</v>
+      </c>
+      <c r="B28" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>1.2477934782608695</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +820,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C491D8-0FDD-41D9-B288-CF2B2F492504}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -859,41 +828,41 @@
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30">
       <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="15" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>121</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>876</v>
       </c>
       <c r="D4" s="2">
@@ -901,14 +870,14 @@
         <v>0.13812785388127855</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="14">
+        <v>29</v>
+      </c>
+      <c r="B5" s="12">
         <v>360</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>5137</v>
       </c>
       <c r="D5" s="2">
@@ -916,14 +885,14 @@
         <v>7.0079813120498352E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="14">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12">
         <v>191</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>1106</v>
       </c>
       <c r="D6" s="2">
@@ -931,77 +900,77 @@
         <v>0.17269439421338156</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30">
+      <c r="A15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="15"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="14">
+        <v>36</v>
+      </c>
+      <c r="B16" s="12">
         <v>69.698999999999998</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="12">
         <f>B16*About!$A$28</f>
         <v>86.969957641304347</v>
       </c>
-      <c r="D16" s="14"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="14">
+        <v>37</v>
+      </c>
+      <c r="B17" s="12">
         <v>34.746000000000002</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="12">
         <f>B17*About!$A$28</f>
         <v>43.355832195652177</v>
       </c>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="14">
+        <v>38</v>
+      </c>
+      <c r="B18" s="12">
         <v>50.64</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <f>B18*About!$A$28</f>
         <v>63.188261739130432</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +984,7 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
@@ -1023,126 +992,295 @@
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="30">
       <c r="A1" s="9" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="17">
+        <v>44</v>
+      </c>
+      <c r="B2" s="14">
         <f>Data!$D$5</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="14">
         <f>$B2</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="14">
         <f>$B2</f>
         <v>7.0079813120498352E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="17">
+        <v>45</v>
+      </c>
+      <c r="B3" s="14">
         <f>Data!$D$5</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="14">
         <f t="shared" ref="C3:D7" si="0">$B3</f>
         <v>7.0079813120498352E-2</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <f t="shared" si="0"/>
         <v>7.0079813120498352E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="11">
+        <v>46</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="11">
+        <v>47</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="17">
+        <v>48</v>
+      </c>
+      <c r="B6" s="14">
         <f>Data!D4</f>
         <v>0.13812785388127855</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <f t="shared" si="0"/>
         <v>0.13812785388127855</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <f t="shared" si="0"/>
         <v>0.13812785388127855</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="11">
+        <v>49</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+    <row r="8" spans="1:4">
       <c r="D8" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8706A5-F512-4FBA-B9FE-B0BD4F88CADD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6AD118-6158-403B-A6B6-F3AC293A46D0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0AB1AFD-2402-466F-9548-69C34C9436B5}"/>
 </file>